--- a/artfynd/A 14308-2026 artfynd.xlsx
+++ b/artfynd/A 14308-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106407802</v>
+        <v>99605488</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vägen ner mot ryggen. , Dlr</t>
+          <t>Avverkad yckelbiotop Timmertjärn, Ryggen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549500.8333282399</v>
+        <v>549264</v>
       </c>
       <c r="R2" t="n">
-        <v>6716734.427129107</v>
+        <v>6716637</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I skogen bredvid vägen. Sågs flera gånger. Svarade även på lockpipa.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,18 +767,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Danielsson, Olle Valseth Danielsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Kajsa Larsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,12 +789,7 @@
         <v>106406904</v>
       </c>
       <c r="B3" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549500.8333282399</v>
+        <v>549501</v>
       </c>
       <c r="R3" t="n">
-        <v>6716734.427129107</v>
+        <v>6716734</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -929,32 +906,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404655</v>
+        <v>99708754</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,32 +934,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abborrmyran, Dlr</t>
+          <t>Väg mot Ryggen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549114</v>
+        <v>549116</v>
       </c>
       <c r="R4" t="n">
-        <v>6716416</v>
+        <v>6716396</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,27 +975,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Svarade på lockpipa</t>
+          <t>Både såg och hörde spillkråkan knappt 50 m bort.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,15 +1010,613 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99708823</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abnorrvalen väster, Ryggen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549104</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6716392</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkan en längre stund när den flög i närheten på ca 50 m avstånd ungefär vid myren.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98449005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägen ner mot ryggen. , Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549501</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6716734</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I talltopp på hygge</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anders Danielsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Olle Valseth Danielsson, Anders Danielsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Danielsson, Olle Valseth Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106407802</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vägen ner mot ryggen. , Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549501</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6716734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-02-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-02-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I skogen bredvid vägen. Sågs flera gånger. Svarade även på lockpipa.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Danielsson, Olle Valseth Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122404655</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Abborrmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549114</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6716416</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Svarade på lockpipa</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Danielsson, Olle Valseth Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99708839</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Abborrvalen väster, Ryggen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549114</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6716398</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14308-2026 artfynd.xlsx
+++ b/artfynd/A 14308-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99605488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106406904</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99708754</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99708823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98449005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106407802</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1507,6 +1542,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122404655</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,8 +1657,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99708839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>